--- a/product-definitions/spreadsheet/aerosol-concentration.xlsx
+++ b/product-definitions/spreadsheet/aerosol-concentration.xlsx
@@ -120,7 +120,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -151,11 +151,6 @@
     <font>
       <color theme="1"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <color rgb="FF000000"/>
@@ -193,17 +188,17 @@
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -1765,7 +1760,7 @@
       <c r="D20" s="12"/>
       <c r="E20" s="12"/>
     </row>
-    <row r="21">
+    <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="2"/>
       <c r="B21" s="5" t="s">
         <v>31</v>
